--- a/Map/USDM2FHIR.xlsx
+++ b/Map/USDM2FHIR.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\USDM_db\Map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864766BC-2522-404A-85B4-A39425393F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1146B2-09EC-457C-9B40-42CABA08DAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4545" yWindow="-16080" windowWidth="26250" windowHeight="14925" xr2:uid="{97BCDFE6-590C-45E1-8F75-1AA7EE2945FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{97BCDFE6-590C-45E1-8F75-1AA7EE2945FF}"/>
   </bookViews>
   <sheets>
     <sheet name="USDM2FHIR map" sheetId="1" r:id="rId1"/>
     <sheet name="ReadMe" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'USDM2FHIR map'!$A$1:$G$85</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -922,27 +925,13 @@
     <t>Translated titles</t>
   </si>
   <si>
-    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="http://cdisc.org/usdm/extensions/extensionR-1/class-1"])@$tr.
-{$tr.id: $tr.extensionAttributes[url="text"].valueString}</t>
-  </si>
-  <si>
     <t>extension</t>
   </si>
   <si>
     <t>Translated title type</t>
   </si>
   <si>
-    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="http://cdisc.org/usdm/extensions/extensionR-1/class-1"])@$tr.
-(   $titleCode := function($c) {$c="C207616" ? "official" : $c="C207615" ? "short-title" :$c="C94108" ? "acronym" : $c="C207618" ? "scientific"};
-    $titleDisplay := function($c) {$c="C207616" ? "Official title" : $c="C207615" ? "Short title" :$c="C94108" ? "Acronym"  : $c="C207618" ? "Scientific title"};
-    {$tr.id: {"code": $titleCode($tt.type.code), "display": $titleDisplay($tt.type.code), "system":"http://hl7.org/fhir/title-type"}})</t>
-  </si>
-  <si>
     <t>Translated title language</t>
-  </si>
-  <si>
-    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="http://cdisc.org/usdm/extensions/extensionR-1/class-1"])@$tr.
-{$tr.id: $tr.extensionAttributes[url="language"].valueCode.code}</t>
   </si>
   <si>
     <t>label.language</t>
@@ -979,19 +968,6 @@
   </si>
   <si>
     <t>progress status period</t>
-  </si>
-  <si>
-    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="https://cdisc.org/usdm/extension-studyProgressStatus/class1"])@$rp.$rp.extensionAttributes[url="https://cdisc.org/usdm/extension-studyProgressStatus-1/attribute-state"].
-{$rp.id:{"code": valueCode.code, "display": valueCode.decode, "system": valueCode.codeSystem}}</t>
-  </si>
-  <si>
-    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="https://cdisc.org/usdm/extension-studyProgressStatus/class1"])@$rp.$rp.extensionAttributes[url="https://cdisc.org/usdm/extension-studyProgressStatus-1/attribute-isActive"].
-{$rp.id:valueBoolean}</t>
-  </si>
-  <si>
-    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="https://cdisc.org/usdm/extension-studyProgressStatus/class1"])@$rp.
-{$rp.id: {"start" : $rp.extensionAttributes[url="https://cdisc.org/usdm/extension-studyProgressStatus-1/attribute-startDate"].valueString,
-            "end" : $rp.extensionAttributes[url="https://cdisc.org/usdm/extension-studyProgressStatus-1/attribute-endDate"].valueString}}</t>
   </si>
   <si>
     <t>progressStatus.period</t>
@@ -1219,81 +1195,108 @@
     <t>Evidence classifier (note that questionnaires should get another code / not taken care of yet)</t>
   </si>
   <si>
+    <t>Outcome measurement display</t>
+  </si>
+  <si>
+    <t>Outcome measurement reference or display</t>
+  </si>
+  <si>
+    <t>objective.outcomeMeasure.endpoint</t>
+  </si>
+  <si>
+    <t>Eligibility criteria code</t>
+  </si>
+  <si>
+    <t>characteristic.code.text</t>
+  </si>
+  <si>
+    <t>EligibilityCriterionItem</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.eligibilityCriteria.{id: label}</t>
+  </si>
+  <si>
+    <t>Arm name</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.arms.label</t>
+  </si>
+  <si>
+    <t>comparisonGroup</t>
+  </si>
+  <si>
+    <t>comparisonGroup.name</t>
+  </si>
+  <si>
+    <t>StudyArm</t>
+  </si>
+  <si>
+    <t>Arm description</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.arms.description</t>
+  </si>
+  <si>
+    <t>comparisonGroup.description</t>
+  </si>
+  <si>
+    <t>Cohort name</t>
+  </si>
+  <si>
+    <t>Cohort description</t>
+  </si>
+  <si>
+    <t>Cohort planned number</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.population.cohorts.label</t>
+  </si>
+  <si>
+    <t>studyCohort</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.population.cohorts.description</t>
+  </si>
+  <si>
+    <t>study.versions.studyDesigns.population.cohorts.plannedEnrollmentNumber.value</t>
+  </si>
+  <si>
+    <t>comparisonGroup.targetNumber</t>
+  </si>
+  <si>
+    <t>plannedEnrollmentNumber</t>
+  </si>
+  <si>
+    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/Translation/v1/Instance"])@$tr.
+{$tr.id: $tr.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/Translation/v1/Instance/text"].valueString}</t>
+  </si>
+  <si>
+    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/Translation/v1/Instance"])@$tr.
+(   $titleCode := function($c) {$c="C207616" ? "official" : $c="C207615" ? "short-title" :$c="C94108" ? "acronym" : $c="C207618" ? "scientific"};
+    $titleDisplay := function($c) {$c="C207616" ? "Official title" : $c="C207615" ? "Short title" :$c="C94108" ? "Acronym"  : $c="C207618" ? "Scientific title"};
+    {$tr.id: {"code": $titleCode($tt.type.code), "display": $titleDisplay($tt.type.code), "system":"http://hl7.org/fhir/title-type"}})</t>
+  </si>
+  <si>
+    <t>study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/Translation/v1/Instance"])@$tr.
+{$tr.id: $tr.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/Translation/v1/Instance/language"].valueCode.code}</t>
+  </si>
+  <si>
     <t>study.versions.studyDesigns.objectives@$ob.$ob.endpoints.(
-    $bcId := extensionAttributes[url="https://cdisc.org/usdm/extension-ExpResponse-1/attribute-relatedAssessment"].valueId;
-    {$ob.id: $bcId ? {"reference": "#" &amp; extensionAttributes[url="https://cdisc.org/usdm/extension-ExpResponse-1/attribute-relatedAssessment"].valueId, "type": "EvidenceVariable" }})</t>
-  </si>
-  <si>
-    <t>Outcome measurement display</t>
-  </si>
-  <si>
-    <t>Outcome measurement reference or display</t>
-  </si>
-  <si>
-    <t>objective.outcomeMeasure.endpoint</t>
-  </si>
-  <si>
-    <t>Eligibility criteria code</t>
-  </si>
-  <si>
-    <t>characteristic.code.text</t>
-  </si>
-  <si>
-    <t>EligibilityCriterionItem</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.eligibilityCriteria.{id: label}</t>
-  </si>
-  <si>
-    <t>Arm name</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.arms.label</t>
-  </si>
-  <si>
-    <t>comparisonGroup</t>
-  </si>
-  <si>
-    <t>comparisonGroup.name</t>
-  </si>
-  <si>
-    <t>StudyArm</t>
-  </si>
-  <si>
-    <t>Arm description</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.arms.description</t>
-  </si>
-  <si>
-    <t>comparisonGroup.description</t>
-  </si>
-  <si>
-    <t>Cohort name</t>
-  </si>
-  <si>
-    <t>Cohort description</t>
-  </si>
-  <si>
-    <t>Cohort planned number</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.population.cohorts.label</t>
-  </si>
-  <si>
-    <t>studyCohort</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.population.cohorts.description</t>
-  </si>
-  <si>
-    <t>study.versions.studyDesigns.population.cohorts.plannedEnrollmentNumber.value</t>
-  </si>
-  <si>
-    <t>comparisonGroup.targetNumber</t>
-  </si>
-  <si>
-    <t>plannedEnrollmentNumber</t>
+    $bcId := extensionAttributes[url="//ExtensionLibrary/USDMv4_0/EndpointReference/v1/forAssessment"].valueId;
+    {$ob.id: $bcId ? {"reference": "#" &amp; extensionAttributes[url="//ExtensionLibrary/USDMv4_0/EndpointReference/v1/forAssessment"].valueId, "type": "EvidenceVariable" }})</t>
+  </si>
+  <si>
+    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance"])@$rp.$rp.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance/state"].
+{$rp.id:{"code": valueCode.code, "display": valueCode.decode, "system": valueCode.codeSystem}}</t>
+  </si>
+  <si>
+    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance"])@$rp.$rp.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance/isActive"].
+{$rp.id:valueBoolean}</t>
+  </si>
+  <si>
+    <t>(study.versions.extensionAttributes.extensionAttributes.valueExtensionClass[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance"])@$rp.
+{$rp.id: {"start" : $rp.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance/startDate"].valueString,
+            "end" : $rp.extensionAttributes[url="//ExtensionLibrary/USDMv4_0/studyProgressStatus/v1/Instance/endDate"].valueString}}</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1379,7 +1382,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1777,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
         <v>161</v>
@@ -1820,16 +1822,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
         <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1843,7 +1845,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
         <v>161</v>
@@ -1866,7 +1868,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C7" t="s">
         <v>161</v>
@@ -1969,7 +1971,7 @@
         <v>233</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="C12" t="s">
         <v>161</v>
@@ -1984,15 +1986,15 @@
         <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="C13" t="s">
         <v>161</v>
@@ -2012,16 +2014,16 @@
     </row>
     <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>239</v>
+        <v>330</v>
       </c>
       <c r="C14" t="s">
         <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -2030,7 +2032,7 @@
         <v>118</v>
       </c>
       <c r="G14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -2081,10 +2083,10 @@
     </row>
     <row r="17" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
         <v>161</v>
@@ -2099,15 +2101,15 @@
         <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C18" t="s">
         <v>161</v>
@@ -2122,15 +2124,15 @@
         <v>129</v>
       </c>
       <c r="G18" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
         <v>161</v>
@@ -2150,10 +2152,10 @@
     </row>
     <row r="20" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C20" t="s">
         <v>161</v>
@@ -2173,10 +2175,10 @@
     </row>
     <row r="21" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C21" t="s">
         <v>161</v>
@@ -2196,10 +2198,10 @@
     </row>
     <row r="22" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
         <v>161</v>
@@ -2219,10 +2221,10 @@
     </row>
     <row r="23" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C23" t="s">
         <v>161</v>
@@ -2420,16 +2422,16 @@
     </row>
     <row r="32" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C32" t="s">
         <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E32" t="s">
         <v>58</v>
@@ -2443,7 +2445,7 @@
     </row>
     <row r="33" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>73</v>
@@ -2452,7 +2454,7 @@
         <v>161</v>
       </c>
       <c r="D33" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -2466,7 +2468,7 @@
         <v>227</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
         <v>161</v>
@@ -2486,10 +2488,10 @@
     </row>
     <row r="35" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C35" t="s">
         <v>161</v>
@@ -2501,18 +2503,18 @@
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C36" t="s">
         <v>161</v>
@@ -2524,10 +2526,10 @@
         <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -2552,186 +2554,186 @@
     </row>
     <row r="38" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C38" t="s">
-        <v>161</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="G38" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="E38" t="s">
-        <v>244</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="C39" t="s">
         <v>161</v>
       </c>
       <c r="D39" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E39" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="C40" t="s">
         <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E40" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C41" t="s">
         <v>161</v>
       </c>
       <c r="D41" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E41" t="s">
-        <v>320</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G41" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F41" t="s">
+        <v>315</v>
+      </c>
+      <c r="G41" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C42" t="s">
         <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E42" t="s">
-        <v>320</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G42" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F42" t="s">
+        <v>315</v>
+      </c>
+      <c r="G42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
       </c>
       <c r="D43" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E43" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="G43" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C44" t="s">
         <v>161</v>
       </c>
       <c r="D44" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E44" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="G44" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G44" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C45" t="s">
         <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E45" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>334</v>
+        <v>323</v>
+      </c>
+      <c r="G45" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2739,7 +2741,7 @@
         <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s">
         <v>161</v>
@@ -2830,7 +2832,7 @@
         <v>207</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s">
         <v>161</v>
@@ -2887,27 +2889,27 @@
         <v>153</v>
       </c>
       <c r="F54" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C55" t="s">
         <v>166</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E55" t="s">
         <v>153</v>
       </c>
       <c r="F55" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -2938,7 +2940,7 @@
         <v>170</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C57" t="s">
         <v>166</v>
@@ -3448,13 +3450,13 @@
     </row>
     <row r="81" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C81" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D81" t="s">
         <v>38</v>
@@ -3462,13 +3464,13 @@
     </row>
     <row r="82" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C82" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D82" t="s">
         <v>213</v>
@@ -3476,13 +3478,13 @@
     </row>
     <row r="83" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C83" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D83" t="s">
         <v>77</v>
@@ -3490,13 +3492,13 @@
     </row>
     <row r="84" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C84" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D84" t="s">
         <v>22</v>
@@ -3504,23 +3506,25 @@
     </row>
     <row r="85" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C85" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G85" xr:uid="{81DD2990-A668-4ED7-89E0-40F5440ED267}"/>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{546F8543-000B-4AD4-8472-81E6831062E9}"/>
-    <hyperlink ref="B34" r:id="rId2" display="study.versions.studyDesigns.objectives@$ob.$ob.endpoints[level.code=&quot;C94496&quot;].{$ob.id: &quot;primary&quot;}" xr:uid="{74E81704-A140-48FF-9D58-8B18F3C8EA13}"/>
-    <hyperlink ref="B33" r:id="rId3" xr:uid="{99798F78-4BAF-4D31-B44E-B30A0F19703D}"/>
+    <hyperlink ref="B34" r:id="rId1" display="study.versions.studyDesigns.objectives@$ob.$ob.endpoints[level.code=&quot;C94496&quot;].{$ob.id: &quot;primary&quot;}" xr:uid="{74E81704-A140-48FF-9D58-8B18F3C8EA13}"/>
+    <hyperlink ref="B33" r:id="rId2" xr:uid="{99798F78-4BAF-4D31-B44E-B30A0F19703D}"/>
+    <hyperlink ref="B12" r:id="rId3" display="study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url=&quot;//ExtensionLibrary/USDMv4_0/Translation/v1/Instance&quot;])@$tr._x000a_{$tr.id: $tr.extensionAttributes[url=&quot;//ExtensionLibrary/USDMv4_0/Translation/v1/Instance/text&quot;].valueString}" xr:uid="{546F8543-000B-4AD4-8472-81E6831062E9}"/>
+    <hyperlink ref="B14" r:id="rId4" display="study.versions.titles@$tt.($tt.extensionAttributes.extensionAttributes.valueExtensionClass[url=&quot;//ExtensionLibrary/USDMv4_0/Translation/v1/Instance&quot;])@$tr._x000a_{$tr.id: $tr.extensionAttributes[url=&quot;//ExtensionLibrary/USDMv4_0/Translation/v1/Instance/language&quot;].valueCode.code}" xr:uid="{7C7BD904-BFC2-41FE-9E5E-787297FFD707}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3595,7 +3599,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -3621,7 +3625,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -3687,7 +3691,7 @@
         <v>145</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -3752,12 +3756,12 @@
     </row>
     <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="B48" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
@@ -3782,30 +3786,30 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B56" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3818,6 +3822,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c40ffa35-e506-4eb9-af8f-b5d6f9d0d5e4">
@@ -3828,7 +3841,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100527ED9A1E2F34D48AA5925CCBA0CEC41" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73c2da0cd5c8d9fd369ff3018c825410">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c40ffa35-e506-4eb9-af8f-b5d6f9d0d5e4" xmlns:ns3="985d26ac-cf7b-4687-94e0-26b141782da7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3600b0f37fd05e6cabe55b41d10e7dc" ns2:_="" ns3:_="">
     <xsd:import namespace="c40ffa35-e506-4eb9-af8f-b5d6f9d0d5e4"/>
@@ -4023,16 +4036,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12DB76A7-ED98-4EE3-9432-17F601352CF4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E61FE636-68A4-4725-8134-F4B9672BB2E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -4049,7 +4061,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9675DCA-D684-4E4E-B61D-0AB2D6821582}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4066,12 +4078,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12DB76A7-ED98-4EE3-9432-17F601352CF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>